--- a/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260615.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260615.xlsx
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>1,642,000</t>
+          <t>11,635,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>11,635,000</t>
+          <t>1,642,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>富喬</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>107,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>富喬</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>107,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
